--- a/tools/precos/planilhas/precos-oficiais-VT-Cosmetics.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-VT-Cosmetics.xlsx
@@ -41,12 +41,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F4E8"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -72,7 +77,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +86,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -582,7 +588,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -637,7 +643,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -690,7 +696,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -743,7 +749,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -778,12 +784,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB003004</t>
+          <t>MB003003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ceramide Aqua Cleansing Oil: óleo de limpeza hidratante com ceramida 200 ml</t>
+          <t>Cica Collagen Essence: essência de colágeno e centella 30 ml</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -792,24 +798,24 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>117.9</v>
+        <v>146.9</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ceramide Cleansing Oil</t>
+          <t>Cica Collagen Essence</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" s="4" t="n">
-        <v>19.01</v>
+        <v>20.16</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>21.12</v>
+        <v>28.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -818,7 +824,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/ceramide-cleansing-oil</t>
+          <t>https://globalvt-cosmetics.com/products/cica-collagen-essence</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -833,12 +839,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB003003</t>
+          <t>MB003002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cica Collagen Essence: essência de colágeno e centella 30 ml</t>
+          <t>Cica Collagen Eyecream: creme para olhos com colágeno e aplicador vibratório 15 ml</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -847,24 +853,24 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>146.9</v>
+        <v>144.9</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cica Collagen Essence</t>
+          <t>Cica Collagen Eyecream</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>20.16</v>
+        <v>20.74</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>28.8</v>
+        <v>25.92</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -873,7 +879,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/cica-collagen-essence</t>
+          <t>https://globalvt-cosmetics.com/products/cica-collagen-eyecream</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -888,12 +894,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB003002</t>
+          <t>MB003001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cica Collagen Eyecream: creme para olhos com colágeno e aplicador vibratório 15 ml</t>
+          <t>Cica Collagen Mask: máscara facial diária de colágeno e cica, 30 unidades</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -902,16 +908,16 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>144.9</v>
+        <v>150.9</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cica Collagen Eyecream</t>
+          <t>Cica Collagen Mask - 30pcs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -919,7 +925,7 @@
         <v>20.74</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>25.92</v>
+        <v>23.04</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -928,7 +934,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/cica-collagen-eyecream</t>
+          <t>https://globalvt-cosmetics.com/products/vt-cica-collagen-mask-30pcs</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -943,12 +949,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB003001</t>
+          <t>MB003000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cica Collagen Mask: máscara facial diária de colágeno e cica, 30 unidades</t>
+          <t>Cica Cream Plus: creme calmante de centella 100 ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -957,16 +963,16 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>150.9</v>
+        <v>144.9</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cica Collagen Mask - 30pcs</t>
+          <t>Cica Cream Plus 100</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -974,7 +980,7 @@
         <v>20.74</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>23.04</v>
+        <v>34.56</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -983,7 +989,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-cica-collagen-mask-30pcs</t>
+          <t>https://globalvt-cosmetics.com/products/cica-cream-plus-100</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -998,12 +1004,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB003000</t>
+          <t>MB002998</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cica Cream Plus: creme calmante de centella 100 ml</t>
+          <t>Cica Mask Cleanser: limpador e máscara de argila com centella e retinol 120 ml</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1012,24 +1018,24 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>144.9</v>
+        <v>147.9</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cica Cream Plus 100</t>
+          <t>Cica Mask Cleanser</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" s="4" t="n">
-        <v>20.74</v>
+        <v>20.16</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>34.56</v>
+        <v>26.88</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1038,7 +1044,7 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/cica-cream-plus-100</t>
+          <t>https://globalvt-cosmetics.com/products/cica-mask-cleanser</t>
         </is>
       </c>
       <c r="L10" s="2">
@@ -1053,12 +1059,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB002998</t>
+          <t>MB002997</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cica Mask Cleanser: limpador e máscara de argila com centella e retinol 120 ml</t>
+          <t>Cica Reti-A Mask: máscara facial diária com retinol e cica, 30 unidades</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1067,24 +1073,24 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>147.9</v>
+        <v>150.9</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cica Mask Cleanser</t>
+          <t>Cica Reti-A Mask - 30pcs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" s="4" t="n">
-        <v>20.16</v>
+        <v>20.74</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>26.88</v>
+        <v>23.04</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1093,7 +1099,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/cica-mask-cleanser</t>
+          <t>https://globalvt-cosmetics.com/products/vt-cica-reti-a-mask-30pcs</t>
         </is>
       </c>
       <c r="L11" s="2">
@@ -1108,12 +1114,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB002997</t>
+          <t>MB002996</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cica Reti-A Mask: máscara facial diária com retinol e cica, 30 unidades</t>
+          <t>Collagen Reedle Shot 100: sérum de colágeno com CICA REEDLE 50 ml</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1122,24 +1128,24 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>150.9</v>
+        <v>257.9</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cica Reti-A Mask - 30pcs</t>
+          <t>Collagen reedle shot 100</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" s="4" t="n">
-        <v>20.74</v>
+        <v>34.56</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>23.04</v>
+        <v>46.08</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1148,7 +1154,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-cica-reti-a-mask-30pcs</t>
+          <t>https://globalvt-cosmetics.com/products/collagen-reedle-shot-100</t>
         </is>
       </c>
       <c r="L12" s="2">
@@ -1163,12 +1169,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB002996</t>
+          <t>MB002993</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Collagen Reedle Shot 100: sérum de colágeno com CICA REEDLE 50 ml</t>
+          <t>Garlic AC Reedle Shot Gel Cream: gel-creme calmante com alho e niacinamida 50 ml</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1177,25 +1183,23 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>257.9</v>
+        <v>181.9</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Collagen reedle shot 100</t>
+          <t>Garlic AC Reedle Shot Gel Cream</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" s="4" t="n">
-        <v>34.56</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>46.08</v>
-      </c>
+        <v>20.16</v>
+      </c>
+      <c r="I13" s="4" t="n"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1203,7 +1207,7 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/collagen-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-gel-cream</t>
         </is>
       </c>
       <c r="L13" s="2">
@@ -1218,12 +1222,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB002993</t>
+          <t>MB002991</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Garlic AC Reedle Shot Gel Cream: gel-creme calmante com alho e niacinamida 50 ml</t>
+          <t>Garlic AC Reedle Shot Spot Cream: creme localizado com alho e tea tree 15 ml</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1232,21 +1236,21 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>181.9</v>
+        <v>132.9</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garlic AC Reedle Shot Gel Cream</t>
+          <t>Garlic AC Reedle Shot Spot Cream</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" s="4" t="n">
-        <v>20.16</v>
+        <v>14.4</v>
       </c>
       <c r="I14" s="4" t="n"/>
       <c r="J14" t="inlineStr">
@@ -1256,7 +1260,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-gel-cream</t>
+          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-spot-cream</t>
         </is>
       </c>
       <c r="L14" s="2">
@@ -1271,12 +1275,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB002991</t>
+          <t>MB002985</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Garlic AC Reedle Shot Spot Cream: creme localizado com alho e tea tree 15 ml</t>
+          <t>Glycolic Reedle Shot Head To Toe Mist: bruma esfoliante com 7% de ácido glicólico 120 ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1285,23 +1289,25 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>132.9</v>
+        <v>123.9</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garlic AC Reedle Shot Spot Cream</t>
+          <t>Glycolic Reedle Shot Head To Toe Mist</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I15" s="4" t="n"/>
+        <v>19.01</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>21.12</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1309,7 +1315,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-spot-cream</t>
+          <t>https://globalvt-cosmetics.com/products/glycolic-reedle-shot-head-to-toe-mist</t>
         </is>
       </c>
       <c r="L15" s="2">
@@ -1324,12 +1330,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB002989</t>
+          <t>MB002984</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Glucamune Cream: creme hidratante de cogumelo tremella 100 ml</t>
+          <t>Hydrop Reedle Shot 100: sérum hidratante com ácido hialurônico e CICA REEDLE 50 ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1338,24 +1344,24 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>133.9</v>
+        <v>240.9</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Glucamune cream</t>
+          <t>Hydrop reedle shot 100</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" s="4" t="n">
-        <v>19.2</v>
+        <v>29.18</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>24</v>
+        <v>30.72</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1364,7 +1370,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/glucamune-cream</t>
+          <t>https://globalvt-cosmetics.com/products/hydrop-reedle-shot-100</t>
         </is>
       </c>
       <c r="L16" s="2">
@@ -1379,12 +1385,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB002988</t>
+          <t>MB002981</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Glucamune Essence: essência hidratante de cogumelo tremella 100 ml</t>
+          <t>Matcha Cica Layer Serum: sérum bifásico calmante de matcha e centella 30 ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1393,24 +1399,24 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>128.9</v>
+        <v>148.9</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Glucamune essence</t>
+          <t>Matcha CIca Layer Serum</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" s="4" t="n">
-        <v>17.66</v>
+        <v>21.6</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>22.08</v>
+        <v>24</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1419,7 +1425,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/glucamune-essence</t>
+          <t>https://globalvt-cosmetics.com/products/matcha-caca-layer-serum</t>
         </is>
       </c>
       <c r="L17" s="2">
@@ -1434,12 +1440,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB002987</t>
+          <t>MB002980</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Glucamune Mask: máscara facial hidratante de cogumelo tremella, 10 unidades</t>
+          <t>Mild Reedle Shot 50: sérum booster suave para iniciantes e uso diário 50 ml</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1448,24 +1454,24 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>138.9</v>
+        <v>144.9</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Glucamune mask (10EA)</t>
+          <t>Mild Reedle Shot 50</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" s="4" t="n">
-        <v>9.82</v>
+        <v>20.74</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>10.92</v>
+        <v>25.29</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1474,7 +1480,7 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/glucamune-mask</t>
+          <t>https://globalvt-cosmetics.com/products/vt-mild-reedle-shot-50</t>
         </is>
       </c>
       <c r="L18" s="2">
@@ -1489,12 +1495,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB002986</t>
+          <t>MB002978</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Glutathione Glow Cleansing Oil: óleo de limpeza com glutationa e niacinamida 200 ml</t>
+          <t>PDRN Barrier Cleanser: espuma de limpeza de pH baixo com PDRN vegetal 200 ml</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1503,25 +1509,23 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>117.9</v>
+        <v>131.9</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Glutathione Cleansing Oil</t>
+          <t>PDRN Barrier Cleanser</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" s="4" t="n">
-        <v>19.01</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>21.12</v>
-      </c>
+        <v>22.08</v>
+      </c>
+      <c r="I19" s="4" t="n"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1529,7 +1533,7 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/glutathione-cleansing-oil</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-barrier-cleanser</t>
         </is>
       </c>
       <c r="L19" s="2">
@@ -1544,12 +1548,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB002985</t>
+          <t>MB002977</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Glycolic Reedle Shot Head To Toe Mist: bruma esfoliante com 7% de ácido glicólico 120 ml</t>
+          <t>PDRN Capsule Cream: gel-creme com cápsulas de PDRN vegetal 50 ml</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1558,24 +1562,24 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>123.9</v>
+        <v>153.9</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Glycolic Reedle Shot Head To Toe Mist</t>
+          <t>PDRN Capsule Cream</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="4" t="n">
-        <v>19.01</v>
+        <v>21.22</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>21.12</v>
+        <v>32.64</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1584,7 +1588,7 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/glycolic-reedle-shot-head-to-toe-mist</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-capsule-cream-100</t>
         </is>
       </c>
       <c r="L20" s="2">
@@ -1599,12 +1603,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB002984</t>
+          <t>MB002976</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hydrop Reedle Shot 100: sérum hidratante com ácido hialurônico e CICA REEDLE 50 ml</t>
+          <t>PDRN Cream 100: creme com PDRN vegetal e cápsulas de azuleno 50 ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1613,24 +1617,24 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>240.9</v>
+        <v>154.9</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hydrop reedle shot 100</t>
+          <t>PDRN Cream 100</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" s="4" t="n">
-        <v>29.18</v>
+        <v>36.86</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>30.72</v>
+        <v>46.08</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1639,7 +1643,7 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/hydrop-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-cream-100</t>
         </is>
       </c>
       <c r="L21" s="2">
@@ -1654,12 +1658,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB002982</t>
+          <t>MB002975</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Luminous Skin Pack: lâminas tônicas de luminosidade com glutationa, 100 unidades</t>
+          <t>PDRN Essence 100: essência leitosa com 100.000 ppm de PDRN vegetal 30 ml</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1668,23 +1672,25 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>104.9</v>
+        <v>241.9</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LUMINOUS SKIN PACK</t>
+          <t>PDRN Essence 100</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I22" s="4" t="n"/>
+        <v>34.56</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>43.2</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1692,7 +1698,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/luminous-skin-pack</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-essence-100</t>
         </is>
       </c>
       <c r="L22" s="2">
@@ -1707,12 +1713,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB002981</t>
+          <t>MB002974</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Matcha Cica Layer Serum: sérum bifásico calmante de matcha e centella 30 ml</t>
+          <t>PDRN Glow Ampoule: ampola em névoa com PDRN vegetal e ceramidas 100 ml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1721,24 +1727,24 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>148.9</v>
+        <v>167.9</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Matcha CIca Layer Serum</t>
+          <t>PDRN GLOW AMPOULE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" s="4" t="n">
-        <v>21.6</v>
+        <v>23.04</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>24</v>
+        <v>30.72</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1747,7 +1753,7 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/matcha-caca-layer-serum</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-glow-ampoule</t>
         </is>
       </c>
       <c r="L23" s="2">
@@ -1762,12 +1768,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB002980</t>
+          <t>MB002973</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mild Reedle Shot 50: sérum booster suave para iniciantes e uso diário 50 ml</t>
+          <t>PDRN Grinding Cleansing Balm: bálsamo demaquilante com PHA, LHA e PDRN 50 ml</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1776,24 +1782,24 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>144.9</v>
+        <v>156.9</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mild Reedle Shot 50</t>
+          <t>PDRN Grinding Cleansing Balm</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" s="4" t="n">
-        <v>20.74</v>
+        <v>21.5</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>25.29</v>
+        <v>26.88</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1802,7 +1808,7 @@
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-mild-reedle-shot-50</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-grinding-cleansing-balm</t>
         </is>
       </c>
       <c r="L24" s="2">
@@ -1817,12 +1823,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB002979</t>
+          <t>MB002972</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mild Skin Pack: lâminas tônicas calmantes com centella, 100 unidades</t>
+          <t>PDRN Hydrogel Eye Patch: patches de hidrogel para os olhos com PDRN, 60 unidades</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1831,21 +1837,21 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>104.9</v>
+        <v>144.9</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MILD SKIN PACK</t>
+          <t>PDRN Hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" s="4" t="n">
-        <v>14.4</v>
+        <v>22.08</v>
       </c>
       <c r="I25" s="4" t="n"/>
       <c r="J25" t="inlineStr">
@@ -1855,7 +1861,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/mild-skin-pack</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-hydrogel-eye-patch</t>
         </is>
       </c>
       <c r="L25" s="2">
@@ -1870,12 +1876,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB002978</t>
+          <t>MB002970</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PDRN Barrier Cleanser: espuma de limpeza de pH baixo com PDRN vegetal 200 ml</t>
+          <t>PDRN R5 Firming Ampoule: ampola firmadora com PDRN vegetal e cica 30 ml</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1884,23 +1890,25 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>131.9</v>
+        <v>130.9</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PDRN Barrier Cleanser</t>
+          <t>PDRN R5 Firming Ampoule</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" s="4" t="n">
-        <v>22.08</v>
-      </c>
-      <c r="I26" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>24</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -1908,7 +1916,7 @@
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-barrier-cleanser</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-r5-firming-ampoule</t>
         </is>
       </c>
       <c r="L26" s="2">
@@ -1923,12 +1931,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB002977</t>
+          <t>MB002969</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PDRN Capsule Cream: gel-creme com cápsulas de PDRN vegetal 50 ml</t>
+          <t>PDRN Reedle Shot 100: sérum de PDRN vegetal de ginseng com CICA REEDLE 50 ml</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1937,24 +1945,24 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>153.9</v>
+        <v>276.9</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PDRN Capsule Cream</t>
+          <t>PDRN REEDLE SHOT 100</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" s="4" t="n">
-        <v>21.22</v>
+        <v>44.54</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>32.64</v>
+        <v>55.68</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1963,7 +1971,7 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-capsule-cream-100</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-100</t>
         </is>
       </c>
       <c r="L27" s="2">
@@ -1978,12 +1986,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB002976</t>
+          <t>MB002968</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PDRN Cream 100: creme com PDRN vegetal e cápsulas de azuleno 50 ml</t>
+          <t>PDRN Reedle Shot Brush Hair Serum: sérum capilar refrescante com escova 100 ml</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1992,24 +2000,24 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>154.9</v>
+        <v>144.9</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PDRN Cream 100</t>
+          <t>PDRN Reedle Shot Brush Hair Serum</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" s="4" t="n">
-        <v>36.86</v>
+        <v>21.88</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>46.08</v>
+        <v>23.04</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2018,7 +2026,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-cream-100</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-brush-hair-serum</t>
         </is>
       </c>
       <c r="L28" s="2">
@@ -2033,12 +2041,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB002975</t>
+          <t>MB002967</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PDRN Essence 100: essência leitosa com 100.000 ppm de PDRN vegetal 30 ml</t>
+          <t>PDRN Reedle Shot Firming Eye Cream: creme para olhos com PDRN e ponteira vibratória 15 ml</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2047,24 +2055,24 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>241.9</v>
+        <v>276.9</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PDRN Essence 100</t>
+          <t>PDRN Reedle Shot Firming Eye Cream</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" s="4" t="n">
-        <v>34.56</v>
+        <v>27.65</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>43.2</v>
+        <v>30.72</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -2073,7 +2081,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-essence-100</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-firming-eye-cream</t>
         </is>
       </c>
       <c r="L29" s="2">
@@ -2088,12 +2096,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB002974</t>
+          <t>MB002966</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PDRN Glow Ampoule: ampola em névoa com PDRN vegetal e ceramidas 100 ml</t>
+          <t>PDRN Reedle Shot Hair Ampoule 100dL: ampola para couro cabeludo 15 ml</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2102,25 +2110,23 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>167.9</v>
+        <v>137.9</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PDRN GLOW AMPOULE</t>
+          <t>PDRN Reedle Shot Hair Ampoule 100dl</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" s="4" t="n">
-        <v>23.04</v>
-      </c>
-      <c r="I30" s="4" t="n">
         <v>30.72</v>
       </c>
+      <c r="I30" s="4" t="n"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2128,7 +2134,7 @@
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-glow-ampoule</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-hair-ampoule-100dl</t>
         </is>
       </c>
       <c r="L30" s="2">
@@ -2143,12 +2149,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MB002973</t>
+          <t>MB002965</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PDRN Grinding Cleansing Balm: bálsamo demaquilante com PHA, LHA e PDRN 50 ml</t>
+          <t>PDRN Reedle Shot Hair Ampoule 300dL: ampola para couro cabeludo 15 ml</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2157,25 +2163,23 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>156.9</v>
+        <v>293.9</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PDRN Grinding Cleansing Balm</t>
+          <t>PDRN Reedle Shot Hair Ampoule 300dl</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" s="4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>26.88</v>
-      </c>
+        <v>40.32</v>
+      </c>
+      <c r="I31" s="4" t="n"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2183,7 +2187,7 @@
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-grinding-cleansing-balm</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-hair-ampoule-300dl</t>
         </is>
       </c>
       <c r="L31" s="2">
@@ -2198,12 +2202,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MB002972</t>
+          <t>MB002964</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PDRN Hydrogel Eye Patch: patches de hidrogel para os olhos com PDRN, 60 unidades</t>
+          <t>PDRN Reedle Shot Hair Ampoule 700dL: ampola para couro cabeludo 15 ml</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2212,21 +2216,21 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>144.9</v>
+        <v>363.9</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PDRN Hydrogel Eye Patch</t>
+          <t>PDRN Reedle Shot Hair Ampoule 700dl</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" s="4" t="n">
-        <v>22.08</v>
+        <v>49.92</v>
       </c>
       <c r="I32" s="4" t="n"/>
       <c r="J32" t="inlineStr">
@@ -2236,7 +2240,7 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-hydrogel-eye-patch</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-hair-ampoule-700dl</t>
         </is>
       </c>
       <c r="L32" s="2">
@@ -2251,12 +2255,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MB002970</t>
+          <t>MB002963</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PDRN R5 Firming Ampoule: ampola firmadora com PDRN vegetal e cica 30 ml</t>
+          <t>PDRN Reedle Shot Scalp Shampoo: shampoo para couro cabeludo com PDRN 200 ml</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2265,21 +2269,21 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>130.9</v>
+        <v>156.9</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PDRN R5 Firming Ampoule</t>
+          <t>PDRN Reedle Shot Scalp Shampoo</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" s="4" t="n">
-        <v>18</v>
+        <v>21.6</v>
       </c>
       <c r="I33" s="4" t="n">
         <v>24</v>
@@ -2291,7 +2295,7 @@
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-r5-firming-ampoule</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-scalp-shampoo</t>
         </is>
       </c>
       <c r="L33" s="2">
@@ -2306,12 +2310,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MB002969</t>
+          <t>MB002962</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot 100: sérum de PDRN vegetal de ginseng com CICA REEDLE 50 ml</t>
+          <t>PDRN Stick Balm: bálsamo em bastão multifuncional com PDRN e colágeno 9,5 g</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2320,24 +2324,24 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>276.9</v>
+        <v>133.9</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PDRN REEDLE SHOT 100</t>
+          <t>PDRN STICK BALM</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" s="4" t="n">
-        <v>44.54</v>
+        <v>18.43</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>55.68</v>
+        <v>30.72</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2346,7 +2350,7 @@
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-stick-balm</t>
         </is>
       </c>
       <c r="L34" s="2">
@@ -2361,12 +2365,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MB002968</t>
+          <t>MB002961</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Brush Hair Serum: sérum capilar refrescante com escova 100 ml</t>
+          <t>PDRN Tension Toner Pad: discos de tônico elásticos com PDRN, 60 unidades</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2375,25 +2379,23 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>144.9</v>
+        <v>147.9</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Brush Hair Serum</t>
+          <t>PDRN Tension Toner Pad</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>21.88</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>23.04</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="I35" s="4" t="n"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2401,7 +2403,7 @@
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-brush-hair-serum</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-tension-toner-pad</t>
         </is>
       </c>
       <c r="L35" s="2">
@@ -2416,12 +2418,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MB002967</t>
+          <t>MB002959</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Firming Eye Cream: creme para olhos com PDRN e ponteira vibratória 15 ml</t>
+          <t>Pro Cica Reedle Shot 100: sérum calmante com cica e CICA REEDLE 50 ml</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2430,24 +2432,24 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>276.9</v>
+        <v>117.9</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Firming Eye Cream</t>
+          <t>Pro cica reedle shot 100</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" s="4" t="n">
-        <v>27.65</v>
+        <v>36.86</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>30.72</v>
+        <v>46.08</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2456,7 +2458,7 @@
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-firming-eye-cream</t>
+          <t>https://globalvt-cosmetics.com/products/pro-cica-reedle-shot-100</t>
         </is>
       </c>
       <c r="L36" s="2">
@@ -2471,12 +2473,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MB002966</t>
+          <t>MB002957</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Hair Ampoule 100dL: ampola para couro cabeludo 15 ml</t>
+          <t>Pro Cica Spot Patch: adesivos de hidrocoloide com centella para espinhas, 66 unidades</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2485,21 +2487,21 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>137.9</v>
+        <v>39.9</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Hair Ampoule 100dl</t>
+          <t>Pro Cica Spot Patch (66ea)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>30.72</v>
+        <v>7.2</v>
       </c>
       <c r="I37" s="4" t="n"/>
       <c r="J37" t="inlineStr">
@@ -2509,7 +2511,7 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-hair-ampoule-100dl</t>
+          <t>https://globalvt-cosmetics.com/products/pro-cica-spot-patch-66ea</t>
         </is>
       </c>
       <c r="L37" s="2">
@@ -2524,12 +2526,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MB002965</t>
+          <t>MB002955</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Hair Ampoule 300dL: ampola para couro cabeludo 15 ml</t>
+          <t>Red Booster Reedle Shot 100: sérum com sangue-de-dragão e CICA REEDLE 50 ml</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2538,23 +2540,25 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>293.9</v>
+        <v>324.9</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Hair Ampoule 300dl</t>
+          <t>Red Booster Reedle Shot 100</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" s="4" t="n">
-        <v>40.32</v>
-      </c>
-      <c r="I38" s="4" t="n"/>
+        <v>34.56</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>46.08</v>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2562,7 +2566,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-hair-ampoule-300dl</t>
+          <t>https://globalvt-cosmetics.com/products/red-booster-reedle-shot-100</t>
         </is>
       </c>
       <c r="L38" s="2">
@@ -2577,12 +2581,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MB002964</t>
+          <t>MB002921</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Hair Ampoule 700dL: ampola para couro cabeludo 15 ml</t>
+          <t>Reedle Shot 1300: tratamento noturno localizado com CICA REEDLE 8 ml</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2591,23 +2595,25 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>363.9</v>
+        <v>365.9</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Hair Ampoule 700dl</t>
+          <t>VT REEDLE SHOT 1300</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" s="4" t="n">
-        <v>49.92</v>
-      </c>
-      <c r="I39" s="4" t="n"/>
+        <v>45.7</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>65.28</v>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2615,7 +2621,7 @@
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-hair-ampoule-700dl</t>
+          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-1300</t>
         </is>
       </c>
       <c r="L39" s="2">
@@ -2630,12 +2636,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MB002963</t>
+          <t>MB002952</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Scalp Shampoo: shampoo para couro cabeludo com PDRN 200 ml</t>
+          <t>Reedle Shot 300: sérum booster intensivo com CICA REEDLE, a cada 3 dias 50 ml</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2644,24 +2650,24 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>156.9</v>
+        <v>230.9</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PDRN Reedle Shot Scalp Shampoo</t>
+          <t>Reedle Shot 300</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" s="4" t="n">
-        <v>21.6</v>
+        <v>32.2</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>24</v>
+        <v>41.28</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2670,7 +2676,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-reedle-shot-scalp-shampoo</t>
+          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-300</t>
         </is>
       </c>
       <c r="L40" s="2">
@@ -2685,12 +2691,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MB002962</t>
+          <t>MB002950</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PDRN Stick Balm: bálsamo em bastão multifuncional com PDRN e colágeno 9,5 g</t>
+          <t>Reedle Shot 700: tratamento semanal com alta concentração de CICA REEDLE 30 ml</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2699,24 +2705,24 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>133.9</v>
+        <v>311.9</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PDRN STICK BALM</t>
+          <t>Reedle Shot 700</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="4" t="n">
-        <v>18.43</v>
+        <v>34.52</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>30.72</v>
+        <v>55.68</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2725,7 +2731,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-stick-balm</t>
+          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-700</t>
         </is>
       </c>
       <c r="L41" s="2">
@@ -2740,12 +2746,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MB002961</t>
+          <t>MB002943</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PDRN Tension Toner Pad: discos de tônico elásticos com PDRN, 60 unidades</t>
+          <t>Reedle Shot Lip Plumper Beginner: gloss volumizador transparente 4,3 g</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2754,21 +2760,21 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>147.9</v>
+        <v>105.9</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PDRN Tension Toner Pad</t>
+          <t>Reedle shot Lip Plumper_Beginner</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="4" t="n">
-        <v>24</v>
+        <v>14.4</v>
       </c>
       <c r="I42" s="4" t="n"/>
       <c r="J42" t="inlineStr">
@@ -2778,7 +2784,7 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-tension-toner-pad</t>
+          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper_beginner</t>
         </is>
       </c>
       <c r="L42" s="2">
@@ -2793,12 +2799,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MB002960</t>
+          <t>MB002948</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PDRN Toner: tônico hidratante com PDRN vegetal de ginseng 250 ml</t>
+          <t>Reedle Shot Lip Plumper Crystal: gloss volumizador transparente cintilante 4,3 g</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2807,25 +2813,23 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>130.9</v>
+        <v>105.9</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PDRN TONER</t>
+          <t>Reedle Shot Lip Plumper Crystal</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>24</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I43" s="4" t="n"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2833,7 +2837,7 @@
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-toner</t>
+          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper-crystal-1</t>
         </is>
       </c>
       <c r="L43" s="2">
@@ -2848,12 +2852,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MB002959</t>
+          <t>MB002944</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pro Cica Reedle Shot 100: sérum calmante com cica e CICA REEDLE 50 ml</t>
+          <t>Reedle Shot Lip Plumper Expert: gloss volumizador transparente 4,3 g</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2862,25 +2866,23 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>117.9</v>
+        <v>119.9</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pro cica reedle shot 100</t>
+          <t>Reedle shot Lip Plumper-Expert</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="4" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>46.08</v>
-      </c>
+        <v>16.32</v>
+      </c>
+      <c r="I44" s="4" t="n"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2888,7 +2890,7 @@
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pro-cica-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper_expert</t>
         </is>
       </c>
       <c r="L44" s="2">
@@ -2903,12 +2905,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MB002957</t>
+          <t>MB002947</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pro Cica Spot Patch: adesivos de hidrocoloide com centella para espinhas, 66 unidades</t>
+          <t>Reedle Shot Lip Plumper Rose Berry: gloss volumizador rosado natural 4,6 g</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2917,21 +2919,21 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>39.9</v>
+        <v>105.9</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pro Cica Spot Patch (66ea)</t>
+          <t>Reedle Shot Lip Plumper Rose Berry</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" s="4" t="n">
-        <v>7.2</v>
+        <v>14.4</v>
       </c>
       <c r="I45" s="4" t="n"/>
       <c r="J45" t="inlineStr">
@@ -2941,7 +2943,7 @@
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pro-cica-spot-patch-66ea</t>
+          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper-rose-berry</t>
         </is>
       </c>
       <c r="L45" s="2">
@@ -2956,12 +2958,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MB002955</t>
+          <t>MB002946</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Red Booster Reedle Shot 100: sérum com sangue-de-dragão e CICA REEDLE 50 ml</t>
+          <t>Reedle Shot Lip Plumper Twinkle: gloss volumizador com glitter rosa e dourado 4,3 g</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2970,25 +2972,23 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>324.9</v>
+        <v>105.9</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Red Booster Reedle Shot 100</t>
+          <t>Reedle Shot Lip Plumper Twinkle</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="4" t="n">
-        <v>34.56</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>46.08</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I46" s="4" t="n"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/red-booster-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper-twinkle</t>
         </is>
       </c>
       <c r="L46" s="2">
@@ -3011,12 +3011,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MB002953</t>
+          <t>MB002945</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Reedle Shot 100 em sachês: sérum booster diário em tamanho de viagem</t>
+          <t>Reedle Shot Lip Plumper Usagi Pink: gloss volumizador rosa vibrante 4,6 g</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3025,25 +3025,23 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reedle Shot 100</t>
+          <t>Reedle Shot Lip Plumper Usagi Pink</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="4" t="n">
-        <v>27.65</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>30.72</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I47" s="4" t="n"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3051,7 +3049,7 @@
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper-usagi-pink</t>
         </is>
       </c>
       <c r="L47" s="2">
@@ -3066,12 +3064,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MB002954</t>
+          <t>MB002942</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Reedle Shot 100: sérum booster diário com CICA REEDLE e centella 50 ml</t>
+          <t>Reedle Shot Vita-Light Cream: creme de vitaminas com CICA REEDLE 50 ml</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3080,24 +3078,24 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>171.9</v>
+        <v>150.9</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reedle Shot 100</t>
+          <t>Reedle Shot Vita-Light Cream</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="4" t="n">
-        <v>27.65</v>
+        <v>20.16</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>30.72</v>
+        <v>33.6</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -3106,7 +3104,7 @@
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-101</t>
         </is>
       </c>
       <c r="L48" s="2">
@@ -3121,12 +3119,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MB002921</t>
+          <t>MB002940</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Reedle Shot 1300: tratamento noturno localizado com CICA REEDLE 8 ml</t>
+          <t>Reti-A Reedle Shot 100: sérum com retinol, bakuchiol e CICA REEDLE 50 ml</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3135,24 +3133,24 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>365.9</v>
+        <v>356.9</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>VT REEDLE SHOT 1300</t>
+          <t>Reti-a reedle shot 100</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="4" t="n">
-        <v>45.7</v>
+        <v>36.86</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>65.28</v>
+        <v>46.08</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3161,7 +3159,7 @@
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-1300</t>
+          <t>https://globalvt-cosmetics.com/products/reti-a-reedle-shot-100</t>
         </is>
       </c>
       <c r="L49" s="2">
@@ -3176,12 +3174,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MB002952</t>
+          <t>MB002938</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Reedle Shot 300: sérum booster intensivo com CICA REEDLE, a cada 3 dias 50 ml</t>
+          <t>Retinal Peptide Capsule Cream: gel-creme com retinal e peptídeos 50 ml</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3190,24 +3188,24 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>230.9</v>
+        <v>201.9</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reedle Shot 300</t>
+          <t>Retinal Peptide Hyaluronic Capsule Cream</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="4" t="n">
-        <v>32.2</v>
+        <v>21.22</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>41.28</v>
+        <v>32.64</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3216,7 +3214,7 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-300</t>
+          <t>https://globalvt-cosmetics.com/products/retinal-peptide-capsule-cream</t>
         </is>
       </c>
       <c r="L50" s="2">
@@ -3231,12 +3229,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MB002950</t>
+          <t>MB002937</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Reedle Shot 700: tratamento semanal com alta concentração de CICA REEDLE 30 ml</t>
+          <t>Retinal Pro Cream 0.025: creme com 0,025% de retinal 20 ml</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3245,24 +3243,24 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>311.9</v>
+        <v>239.9</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Reedle Shot 700</t>
+          <t>Retinal Pro Cream 0.025</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="4" t="n">
-        <v>34.52</v>
+        <v>28.22</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>55.68</v>
+        <v>31.68</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3271,7 +3269,7 @@
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-700</t>
+          <t>https://globalvt-cosmetics.com/products/retinal-pro-cream-0-025</t>
         </is>
       </c>
       <c r="L51" s="2">
@@ -3286,12 +3284,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MB002949</t>
+          <t>MB002936</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Reedle Shot Firming Eye Cream: creme para olhos com ponteira vibratória 15 ml</t>
+          <t>Retinal Pro Cream 0.05: creme com 0,05% de retinal 20 ml</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3300,24 +3298,24 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>171.9</v>
+        <v>239.9</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reedle Shot Firming Eye Cream</t>
+          <t>Retinal Pro Cream 0.05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="4" t="n">
-        <v>20.74</v>
+        <v>23.52</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>25.92</v>
+        <v>33.6</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3326,7 +3324,7 @@
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reedle-shot-firming-eye-cream</t>
+          <t>https://globalvt-cosmetics.com/products/retinal-pro-cream-0-05</t>
         </is>
       </c>
       <c r="L52" s="2">
@@ -3341,12 +3339,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MB002943</t>
+          <t>MB002934</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Beginner: gloss volumizador transparente 4,3 g</t>
+          <t>Rice Ceramide Capsule Cream: gel-creme de arroz com cápsulas de ceramida 50 ml</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3355,23 +3353,25 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>105.9</v>
+        <v>201.9</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Reedle shot Lip Plumper_Beginner</t>
+          <t>Rice Ceramide Capsule Cream</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I53" s="4" t="n"/>
+        <v>21.22</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>32.64</v>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper_beginner</t>
+          <t>https://globalvt-cosmetics.com/products/rice-ceramide-capsule-cream</t>
         </is>
       </c>
       <c r="L53" s="2">
@@ -3394,12 +3394,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MB002948</t>
+          <t>MB002933</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Crystal: gloss volumizador transparente cintilante 4,3 g</t>
+          <t>Rice Ceramide Serum: sérum leitoso de arroz e ceramidas 30 ml</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3408,23 +3408,25 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>105.9</v>
+        <v>176.9</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Crystal</t>
+          <t>Rice Ceramide Serum</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I54" s="4" t="n"/>
+        <v>24.19</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>26.88</v>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3432,7 +3434,7 @@
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper-crystal-1</t>
+          <t>https://globalvt-cosmetics.com/products/rice-ceramide-serum</t>
         </is>
       </c>
       <c r="L54" s="2">
@@ -3447,12 +3449,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MB002944</t>
+          <t>MB002931</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Expert: gloss volumizador transparente 4,3 g</t>
+          <t>TX-Toning Cream: creme com ácido tranexâmico e glutationa 50 ml</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3461,21 +3463,21 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>119.9</v>
+        <v>223.9</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Reedle shot Lip Plumper-Expert</t>
+          <t>Tx-toning Cream</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="4" t="n">
-        <v>16.32</v>
+        <v>30.72</v>
       </c>
       <c r="I55" s="4" t="n"/>
       <c r="J55" t="inlineStr">
@@ -3485,7 +3487,7 @@
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper_expert</t>
+          <t>https://globalvt-cosmetics.com/products/tx-toning-cream</t>
         </is>
       </c>
       <c r="L55" s="2">
@@ -3500,12 +3502,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MB002947</t>
+          <t>MB002930</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Rose Berry: gloss volumizador rosado natural 4,6 g</t>
+          <t>TX-Toning Daily Mask: máscara diária com ácido tranexâmico, 30 unidades</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3514,21 +3516,21 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>105.9</v>
+        <v>139.9</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Rose Berry</t>
+          <t>Tx-toning Daily Mask</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="4" t="n">
-        <v>14.4</v>
+        <v>24.96</v>
       </c>
       <c r="I56" s="4" t="n"/>
       <c r="J56" t="inlineStr">
@@ -3538,7 +3540,7 @@
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper-rose-berry</t>
+          <t>https://globalvt-cosmetics.com/products/tx-toning-daily-mask</t>
         </is>
       </c>
       <c r="L56" s="2">
@@ -3553,12 +3555,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MB002946</t>
+          <t>MB002929</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Twinkle: gloss volumizador com glitter rosa e dourado 4,3 g</t>
+          <t>TX-Toning Essence 1000 Shot: essência com ácido tranexâmico 30 ml</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3567,23 +3569,25 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>105.9</v>
+        <v>136.9</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Twinkle</t>
+          <t>Tx-toning Essence 1000 shot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I57" s="4" t="n"/>
+        <v>18.82</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>26.88</v>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3591,7 +3595,7 @@
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper-twinkle</t>
+          <t>https://globalvt-cosmetics.com/products/tx-toning-essence-1000-shot</t>
         </is>
       </c>
       <c r="L57" s="2">
@@ -3606,12 +3610,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MB002945</t>
+          <t>MB002928</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Usagi Pink: gloss volumizador rosa vibrante 4,6 g</t>
+          <t>TX-Toning Toner: tônico com ácido tranexâmico e niacinamida 200 ml</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3620,23 +3624,25 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>105.9</v>
+        <v>144.9</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Reedle Shot Lip Plumper Usagi Pink</t>
+          <t>Tx-toning Toner</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I58" s="4" t="n"/>
+        <v>17.66</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>22.08</v>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3644,7 +3650,7 @@
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reedle-shot-lip-plumper-usagi-pink</t>
+          <t>https://globalvt-cosmetics.com/products/tx-toning-toner</t>
         </is>
       </c>
       <c r="L58" s="2">
@@ -3659,12 +3665,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MB002942</t>
+          <t>MB002925</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Reedle Shot Vita-Light Cream: creme de vitaminas com CICA REEDLE 50 ml</t>
+          <t>Vita-Light Reedle Shot 100: sérum de vitamina C com CICA REEDLE 50 ml</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3673,24 +3679,24 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>150.9</v>
+        <v>235.9</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Reedle Shot Vita-Light Cream</t>
+          <t>Vita-light reedle shot 100</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" s="4" t="n">
-        <v>20.16</v>
+        <v>32.26</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>33.6</v>
+        <v>46.08</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3699,7 +3705,7 @@
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-101</t>
+          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-100</t>
         </is>
       </c>
       <c r="L59" s="2">
@@ -3714,12 +3720,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MB002926</t>
+          <t>MB002923</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Reedle Shot Vita-Light Eye Cream: creme para olhos com ponteira vibratória 15 ml</t>
+          <t>Vitamin C Astaxanthin Mask: máscara facial diária de vitamina C, 30 unidades</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3732,20 +3738,20 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Reedle Shot Vita-Light Cream</t>
+          <t>Vitamin C Astaxanthin Mask</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="4" t="n">
-        <v>20.16</v>
+        <v>20.74</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>33.6</v>
+        <v>23.04</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3754,7 +3760,7 @@
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-101</t>
+          <t>https://globalvt-cosmetics.com/products/vitamin-c-astaxanthin-mask</t>
         </is>
       </c>
       <c r="L60" s="2">
@@ -3769,12 +3775,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB002940</t>
+          <t>MB003004</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Reti-A Reedle Shot 100: sérum com retinol, bakuchiol e CICA REEDLE 50 ml</t>
+          <t>Ceramide Aqua Cleansing Oil: óleo de limpeza hidratante com ceramida 200 ml</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3783,24 +3789,24 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>356.9</v>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
+        <v>117.9</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Reti-a reedle shot 100</t>
+          <t>Ceramide Cleansing Oil</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="4" t="n">
-        <v>36.86</v>
+        <v>19.01</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>46.08</v>
+        <v>21.12</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3809,7 +3815,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reti-a-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/ceramide-cleansing-oil</t>
         </is>
       </c>
       <c r="L61" s="2">
@@ -3824,12 +3830,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB002938</t>
+          <t>MB002989</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Retinal Peptide Capsule Cream: gel-creme com retinal e peptídeos 50 ml</t>
+          <t>Glucamune Cream: creme hidratante de cogumelo tremella 100 ml</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3838,24 +3844,24 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>201.9</v>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
+        <v>133.9</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Retinal Peptide Hyaluronic Capsule Cream</t>
+          <t>Glucamune cream</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="4" t="n">
-        <v>21.22</v>
+        <v>19.2</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>32.64</v>
+        <v>24</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3864,7 +3870,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/retinal-peptide-capsule-cream</t>
+          <t>https://globalvt-cosmetics.com/products/glucamune-cream</t>
         </is>
       </c>
       <c r="L62" s="2">
@@ -3879,12 +3885,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB002937</t>
+          <t>MB002988</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Retinal Pro Cream 0.025: creme com 0,025% de retinal 20 ml</t>
+          <t>Glucamune Essence: essência hidratante de cogumelo tremella 100 ml</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3893,24 +3899,24 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>239.9</v>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
+        <v>128.9</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Retinal Pro Cream 0.025</t>
+          <t>Glucamune essence</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="4" t="n">
-        <v>28.22</v>
+        <v>17.66</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>31.68</v>
+        <v>22.08</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3919,7 +3925,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/retinal-pro-cream-0-025</t>
+          <t>https://globalvt-cosmetics.com/products/glucamune-essence</t>
         </is>
       </c>
       <c r="L63" s="2">
@@ -3934,12 +3940,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB002936</t>
+          <t>MB002987</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Retinal Pro Cream 0.05: creme com 0,05% de retinal 20 ml</t>
+          <t>Glucamune Mask: máscara facial hidratante de cogumelo tremella, 10 unidades</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3948,24 +3954,24 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>239.9</v>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
+        <v>138.9</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Retinal Pro Cream 0.05</t>
+          <t>Glucamune mask (10EA)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="4" t="n">
-        <v>23.52</v>
+        <v>9.82</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>33.6</v>
+        <v>10.92</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3974,7 +3980,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/retinal-pro-cream-0-05</t>
+          <t>https://globalvt-cosmetics.com/products/glucamune-mask</t>
         </is>
       </c>
       <c r="L64" s="2">
@@ -3989,12 +3995,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB002935</t>
+          <t>MB002986</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Retinal Pro Cream 0.1: creme com 0,1% de retinal 20 ml</t>
+          <t>Glutathione Glow Cleansing Oil: óleo de limpeza com glutationa e niacinamida 200 ml</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4003,24 +4009,24 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>239.9</v>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
+        <v>117.9</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Retinal Pro Cream 0.1</t>
+          <t>Glutathione Cleansing Oil</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="4" t="n">
-        <v>22.18</v>
+        <v>19.01</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>40.32</v>
+        <v>21.12</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4029,7 +4035,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/retinal-pro-cream-0-1</t>
+          <t>https://globalvt-cosmetics.com/products/glutathione-cleansing-oil</t>
         </is>
       </c>
       <c r="L65" s="2">
@@ -4044,12 +4050,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB002934</t>
+          <t>MB002982</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rice Ceramide Capsule Cream: gel-creme de arroz com cápsulas de ceramida 50 ml</t>
+          <t>Luminous Skin Pack: lâminas tônicas de luminosidade com glutationa, 100 unidades</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4058,25 +4064,23 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>201.9</v>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
+        <v>104.9</v>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rice Ceramide Capsule Cream</t>
+          <t>LUMINOUS SKIN PACK</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="4" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="I66" s="4" t="n">
-        <v>32.64</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I66" s="4" t="n"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4084,7 +4088,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/rice-ceramide-capsule-cream</t>
+          <t>https://globalvt-cosmetics.com/products/luminous-skin-pack</t>
         </is>
       </c>
       <c r="L66" s="2">
@@ -4099,12 +4103,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB002933</t>
+          <t>MB002979</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rice Ceramide Serum: sérum leitoso de arroz e ceramidas 30 ml</t>
+          <t>Mild Skin Pack: lâminas tônicas calmantes com centella, 100 unidades</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4113,25 +4117,23 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>176.9</v>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
+        <v>104.9</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rice Ceramide Serum</t>
+          <t>MILD SKIN PACK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="4" t="n">
-        <v>24.19</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>26.88</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I67" s="4" t="n"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4139,7 +4141,7 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/rice-ceramide-serum</t>
+          <t>https://globalvt-cosmetics.com/products/mild-skin-pack</t>
         </is>
       </c>
       <c r="L67" s="2">
@@ -4154,12 +4156,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MB002932</t>
+          <t>MB002960</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Smooth Skin Pack: lâminas tônicas com retinol, PHA e peptídeos, 100 unidades</t>
+          <t>PDRN Toner: tônico hidratante com PDRN vegetal de ginseng 250 ml</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4168,23 +4170,25 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
+        <v>130.9</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SMOOTH SKIN PACK</t>
+          <t>PDRN TONER</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I68" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>24</v>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4192,7 +4196,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/smooth-skin-pack</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-toner</t>
         </is>
       </c>
       <c r="L68" s="2">
@@ -4207,12 +4211,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MB002931</t>
+          <t>MB002953</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TX-Toning Cream: creme com ácido tranexâmico e glutationa 50 ml</t>
+          <t>Reedle Shot 100 em sachês: sérum booster diário em tamanho de viagem</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4221,23 +4225,25 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>223.9</v>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tx-toning Cream</t>
+          <t>Reedle Shot 100</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="4" t="n">
+        <v>27.65</v>
+      </c>
+      <c r="I69" s="4" t="n">
         <v>30.72</v>
       </c>
-      <c r="I69" s="4" t="n"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4245,7 +4251,7 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/tx-toning-cream</t>
+          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-100</t>
         </is>
       </c>
       <c r="L69" s="2">
@@ -4260,12 +4266,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MB002930</t>
+          <t>MB002954</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TX-Toning Daily Mask: máscara diária com ácido tranexâmico, 30 unidades</t>
+          <t>Reedle Shot 100: sérum booster diário com CICA REEDLE e centella 50 ml</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4274,23 +4280,25 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>139.9</v>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
+        <v>171.9</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tx-toning Daily Mask</t>
+          <t>Reedle Shot 100</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="4" t="n">
-        <v>24.96</v>
-      </c>
-      <c r="I70" s="4" t="n"/>
+        <v>27.65</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>30.72</v>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4298,7 +4306,7 @@
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/tx-toning-daily-mask</t>
+          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-100</t>
         </is>
       </c>
       <c r="L70" s="2">
@@ -4313,12 +4321,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MB002929</t>
+          <t>MB002949</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TX-Toning Essence 1000 Shot: essência com ácido tranexâmico 30 ml</t>
+          <t>Reedle Shot Firming Eye Cream: creme para olhos com ponteira vibratória 15 ml</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4327,24 +4335,24 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>136.9</v>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
+        <v>171.9</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tx-toning Essence 1000 shot</t>
+          <t>Reedle Shot Firming Eye Cream</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="4" t="n">
-        <v>18.82</v>
+        <v>20.74</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>26.88</v>
+        <v>25.92</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4353,7 +4361,7 @@
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/tx-toning-essence-1000-shot</t>
+          <t>https://globalvt-cosmetics.com/products/reedle-shot-firming-eye-cream</t>
         </is>
       </c>
       <c r="L71" s="2">
@@ -4368,12 +4376,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MB002928</t>
+          <t>MB002926</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TX-Toning Toner: tônico com ácido tranexâmico e niacinamida 200 ml</t>
+          <t>Reedle Shot Vita-Light Eye Cream: creme para olhos com ponteira vibratória 15 ml</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4382,24 +4390,24 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
+        <v>151.9</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tx-toning Toner</t>
+          <t>Reedle Shot Vita-Light Cream</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="4" t="n">
-        <v>17.66</v>
+        <v>20.16</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>22.08</v>
+        <v>33.6</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -4408,7 +4416,7 @@
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/tx-toning-toner</t>
+          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-101</t>
         </is>
       </c>
       <c r="L72" s="2">
@@ -4423,12 +4431,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MB002925</t>
+          <t>MB002935</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Vita-Light Reedle Shot 100: sérum de vitamina C com CICA REEDLE 50 ml</t>
+          <t>Retinal Pro Cream 0.1: creme com 0,1% de retinal 20 ml</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4437,24 +4445,24 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>235.9</v>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
+        <v>239.9</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vita-light reedle shot 100</t>
+          <t>Retinal Pro Cream 0.1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="4" t="n">
-        <v>32.26</v>
+        <v>22.18</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>46.08</v>
+        <v>40.32</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -4463,7 +4471,7 @@
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/retinal-pro-cream-0-1</t>
         </is>
       </c>
       <c r="L73" s="2">
@@ -4478,12 +4486,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MB002923</t>
+          <t>MB002932</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vitamin C Astaxanthin Mask: máscara facial diária de vitamina C, 30 unidades</t>
+          <t>Smooth Skin Pack: lâminas tônicas com retinol, PHA e peptídeos, 100 unidades</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4492,25 +4500,23 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>151.9</v>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitamin C Astaxanthin Mask</t>
+          <t>SMOOTH SKIN PACK</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="4" t="n">
-        <v>20.74</v>
-      </c>
-      <c r="I74" s="4" t="n">
-        <v>23.04</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I74" s="4" t="n"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4518,7 +4524,7 @@
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vitamin-c-astaxanthin-mask</t>
+          <t>https://globalvt-cosmetics.com/products/smooth-skin-pack</t>
         </is>
       </c>
       <c r="L74" s="2">
@@ -4549,7 +4555,7 @@
       <c r="D75" s="2" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -4604,7 +4610,7 @@
       <c r="D76" s="2" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -4659,7 +4665,7 @@
       <c r="D77" s="2" t="n">
         <v>48.9</v>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -4712,7 +4718,7 @@
       <c r="D78" s="2" t="n">
         <v>128.9</v>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -4767,7 +4773,7 @@
       <c r="D79" s="2" t="n">
         <v>119.9</v>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -4822,7 +4828,7 @@
       <c r="D80" s="2" t="n">
         <v>154.9</v>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -4877,7 +4883,7 @@
       <c r="D81" s="2" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E81" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -4932,7 +4938,7 @@
       <c r="D82" s="2" t="n">
         <v>119.9</v>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -4987,7 +4993,7 @@
       <c r="D83" s="2" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -5042,7 +5048,7 @@
       <c r="D84" s="2" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -5097,7 +5103,7 @@
       <c r="D85" s="2" t="n">
         <v>119.9</v>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -5152,7 +5158,7 @@
       <c r="D86" s="2" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -5207,7 +5213,7 @@
       <c r="D87" s="2" t="n">
         <v>119.9</v>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -5262,7 +5268,7 @@
       <c r="D88" s="2" t="n">
         <v>155.9</v>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -5317,19 +5323,19 @@
       <c r="D89" s="2" t="n">
         <v>48.9</v>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garlic AC Reedle Shot Gel Cream</t>
+          <t>Garlic AC Reedle shot Spot Patch</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" s="4" t="n">
-        <v>20.16</v>
+        <v>6.72</v>
       </c>
       <c r="I89" s="4" t="n"/>
       <c r="J89" t="inlineStr">
@@ -5339,7 +5345,7 @@
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-gel-cream</t>
+          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-spot-patch</t>
         </is>
       </c>
       <c r="L89" s="2">
@@ -8467,7 +8473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://globalvt-cosmetics.com · loja "VT Cosmetics official" · moeda USD · lido em 30/10/2026 06:02 UTC</t>
+          <t>Site oficial: https://globalvt-cosmetics.com · loja "VT Cosmetics official" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-VT-Cosmetics.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-VT-Cosmetics.xlsx
@@ -8473,7 +8473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://globalvt-cosmetics.com · loja "VT Cosmetics official" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
+          <t>Site oficial: https://globalvt-cosmetics.com · loja "VT Cosmetics official" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-VT-Cosmetics.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-VT-Cosmetics.xlsx
@@ -3775,12 +3775,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MB003004</t>
+          <t>MB002990</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ceramide Aqua Cleansing Oil: óleo de limpeza hidratante com ceramida 200 ml</t>
+          <t>Adesivo Localizado Garlic AC Reedle Shot</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>117.9</v>
+        <v>48.9</v>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
@@ -3798,16 +3798,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ceramide Cleansing Oil</t>
+          <t>Garlic AC Reedle shot Spot Patch</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="4" t="n">
-        <v>19.01</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>21.12</v>
-      </c>
+        <v>6.72</v>
+      </c>
+      <c r="I61" s="4" t="n"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -3815,7 +3813,7 @@
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/ceramide-cleansing-oil</t>
+          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-spot-patch</t>
         </is>
       </c>
       <c r="L61" s="2">
@@ -3830,12 +3828,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MB002989</t>
+          <t>MB003004</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Glucamune Cream: creme hidratante de cogumelo tremella 100 ml</t>
+          <t>Ceramide Aqua Cleansing Oil: óleo de limpeza hidratante com ceramida 200 ml</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3844,7 +3842,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>133.9</v>
+        <v>117.9</v>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
@@ -3853,15 +3851,15 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Glucamune cream</t>
+          <t>Ceramide Cleansing Oil</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="4" t="n">
-        <v>19.2</v>
+        <v>19.01</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>24</v>
+        <v>21.12</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3870,7 +3868,7 @@
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/glucamune-cream</t>
+          <t>https://globalvt-cosmetics.com/products/ceramide-cleansing-oil</t>
         </is>
       </c>
       <c r="L62" s="2">
@@ -3885,12 +3883,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB002988</t>
+          <t>MB002989</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Glucamune Essence: essência hidratante de cogumelo tremella 100 ml</t>
+          <t>Glucamune Cream: creme hidratante de cogumelo tremella 100 ml</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3899,7 +3897,7 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>128.9</v>
+        <v>133.9</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -3908,15 +3906,15 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Glucamune essence</t>
+          <t>Glucamune cream</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="4" t="n">
-        <v>17.66</v>
+        <v>19.2</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>22.08</v>
+        <v>24</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3925,7 +3923,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/glucamune-essence</t>
+          <t>https://globalvt-cosmetics.com/products/glucamune-cream</t>
         </is>
       </c>
       <c r="L63" s="2">
@@ -3940,12 +3938,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB002987</t>
+          <t>MB002988</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Glucamune Mask: máscara facial hidratante de cogumelo tremella, 10 unidades</t>
+          <t>Glucamune Essence: essência hidratante de cogumelo tremella 100 ml</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3954,7 +3952,7 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>138.9</v>
+        <v>128.9</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -3963,15 +3961,15 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Glucamune mask (10EA)</t>
+          <t>Glucamune essence</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="4" t="n">
-        <v>9.82</v>
+        <v>17.66</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>10.92</v>
+        <v>22.08</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3980,7 +3978,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/glucamune-mask</t>
+          <t>https://globalvt-cosmetics.com/products/glucamune-essence</t>
         </is>
       </c>
       <c r="L64" s="2">
@@ -3995,12 +3993,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB002986</t>
+          <t>MB002987</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Glutathione Glow Cleansing Oil: óleo de limpeza com glutationa e niacinamida 200 ml</t>
+          <t>Glucamune Mask: máscara facial hidratante de cogumelo tremella, 10 unidades</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4009,7 +4007,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>117.9</v>
+        <v>138.9</v>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
@@ -4018,15 +4016,15 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Glutathione Cleansing Oil</t>
+          <t>Glucamune mask (10EA)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="4" t="n">
-        <v>19.01</v>
+        <v>9.82</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>21.12</v>
+        <v>10.92</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -4035,7 +4033,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/glutathione-cleansing-oil</t>
+          <t>https://globalvt-cosmetics.com/products/glucamune-mask</t>
         </is>
       </c>
       <c r="L65" s="2">
@@ -4050,12 +4048,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB002982</t>
+          <t>MB002986</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Luminous Skin Pack: lâminas tônicas de luminosidade com glutationa, 100 unidades</t>
+          <t>Glutathione Glow Cleansing Oil: óleo de limpeza com glutationa e niacinamida 200 ml</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4064,7 +4062,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>104.9</v>
+        <v>117.9</v>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
@@ -4073,14 +4071,16 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LUMINOUS SKIN PACK</t>
+          <t>Glutathione Cleansing Oil</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I66" s="4" t="n"/>
+        <v>19.01</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>21.12</v>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/luminous-skin-pack</t>
+          <t>https://globalvt-cosmetics.com/products/glutathione-cleansing-oil</t>
         </is>
       </c>
       <c r="L66" s="2">
@@ -4103,12 +4103,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB002979</t>
+          <t>MB002982</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mild Skin Pack: lâminas tônicas calmantes com centella, 100 unidades</t>
+          <t>Luminous Skin Pack: lâminas tônicas de luminosidade com glutationa, 100 unidades</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MILD SKIN PACK</t>
+          <t>LUMINOUS SKIN PACK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/mild-skin-pack</t>
+          <t>https://globalvt-cosmetics.com/products/luminous-skin-pack</t>
         </is>
       </c>
       <c r="L67" s="2">
@@ -4156,12 +4156,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MB002960</t>
+          <t>MB002979</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PDRN Toner: tônico hidratante com PDRN vegetal de ginseng 250 ml</t>
+          <t>Mild Skin Pack: lâminas tônicas calmantes com centella, 100 unidades</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>130.9</v>
+        <v>104.9</v>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
@@ -4179,16 +4179,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PDRN TONER</t>
+          <t>MILD SKIN PACK</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>24</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I68" s="4" t="n"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4196,7 +4194,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-toner</t>
+          <t>https://globalvt-cosmetics.com/products/mild-skin-pack</t>
         </is>
       </c>
       <c r="L68" s="2">
@@ -4211,12 +4209,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MB002953</t>
+          <t>MB002960</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Reedle Shot 100 em sachês: sérum booster diário em tamanho de viagem</t>
+          <t>PDRN Toner: tônico hidratante com PDRN vegetal de ginseng 250 ml</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4225,7 +4223,7 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>130.9</v>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
@@ -4234,15 +4232,15 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Reedle Shot 100</t>
+          <t>PDRN TONER</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="4" t="n">
-        <v>27.65</v>
+        <v>18</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>30.72</v>
+        <v>24</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4251,7 +4249,7 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-toner</t>
         </is>
       </c>
       <c r="L69" s="2">
@@ -4266,12 +4264,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MB002954</t>
+          <t>MB002953</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Reedle Shot 100: sérum booster diário com CICA REEDLE e centella 50 ml</t>
+          <t>Reedle Shot 100 em sachês: sérum booster diário em tamanho de viagem</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4280,7 +4278,7 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>171.9</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
@@ -4321,12 +4319,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MB002949</t>
+          <t>MB002954</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Reedle Shot Firming Eye Cream: creme para olhos com ponteira vibratória 15 ml</t>
+          <t>Reedle Shot 100: sérum booster diário com CICA REEDLE e centella 50 ml</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4344,15 +4342,15 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Reedle Shot Firming Eye Cream</t>
+          <t>Reedle Shot 100</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="4" t="n">
-        <v>20.74</v>
+        <v>27.65</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>25.92</v>
+        <v>30.72</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -4361,7 +4359,7 @@
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reedle-shot-firming-eye-cream</t>
+          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-100</t>
         </is>
       </c>
       <c r="L71" s="2">
@@ -4376,12 +4374,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MB002926</t>
+          <t>MB002949</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Reedle Shot Vita-Light Eye Cream: creme para olhos com ponteira vibratória 15 ml</t>
+          <t>Reedle Shot Firming Eye Cream: creme para olhos com ponteira vibratória 15 ml</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4390,7 +4388,7 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>151.9</v>
+        <v>171.9</v>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
@@ -4399,15 +4397,15 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reedle Shot Vita-Light Cream</t>
+          <t>Reedle Shot Firming Eye Cream</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="4" t="n">
-        <v>20.16</v>
+        <v>20.74</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>33.6</v>
+        <v>25.92</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -4416,7 +4414,7 @@
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-101</t>
+          <t>https://globalvt-cosmetics.com/products/reedle-shot-firming-eye-cream</t>
         </is>
       </c>
       <c r="L72" s="2">
@@ -4431,12 +4429,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MB002935</t>
+          <t>MB002926</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Retinal Pro Cream 0.1: creme com 0,1% de retinal 20 ml</t>
+          <t>Reedle Shot Vita-Light Eye Cream: creme para olhos com ponteira vibratória 15 ml</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4445,7 +4443,7 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>239.9</v>
+        <v>151.9</v>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
@@ -4454,15 +4452,15 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Retinal Pro Cream 0.1</t>
+          <t>Reedle Shot Vita-Light Cream</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="4" t="n">
-        <v>22.18</v>
+        <v>20.16</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>40.32</v>
+        <v>33.6</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -4471,7 +4469,7 @@
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/retinal-pro-cream-0-1</t>
+          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-101</t>
         </is>
       </c>
       <c r="L73" s="2">
@@ -4486,12 +4484,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MB002932</t>
+          <t>MB002935</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Smooth Skin Pack: lâminas tônicas com retinol, PHA e peptídeos, 100 unidades</t>
+          <t>Retinal Pro Cream 0.1: creme com 0,1% de retinal 20 ml</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4500,7 +4498,7 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>88.90000000000001</v>
+        <v>239.9</v>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
@@ -4509,14 +4507,16 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SMOOTH SKIN PACK</t>
+          <t>Retinal Pro Cream 0.1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I74" s="4" t="n"/>
+        <v>22.18</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>40.32</v>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/smooth-skin-pack</t>
+          <t>https://globalvt-cosmetics.com/products/retinal-pro-cream-0-1</t>
         </is>
       </c>
       <c r="L74" s="2">
@@ -4539,12 +4539,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MB002994</t>
+          <t>MB002932</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Collagen Reedle Shot 100 em sachês: sérum de colágeno 10 x 2 ml</t>
+          <t>Smooth Skin Pack: lâminas tônicas com retinol, PHA e peptídeos, 100 unidades</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4553,25 +4553,23 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Collagen reedle shot 100</t>
+          <t>SMOOTH SKIN PACK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="4" t="n">
-        <v>34.56</v>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>46.08</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="I75" s="4" t="n"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4579,7 +4577,7 @@
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/collagen-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/smooth-skin-pack</t>
         </is>
       </c>
       <c r="L75" s="2">
@@ -4594,12 +4592,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MB002995</t>
+          <t>MB002994</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Collagen Reedle Shot 100: máscara de hidrogel firmadora em 2 passos, 4 unidades</t>
+          <t>Collagen Reedle Shot 100 em sachês: sérum de colágeno 10 x 2 ml</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4608,7 +4606,7 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
@@ -4649,12 +4647,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MB002992</t>
+          <t>MB002995</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Garlic AC Reedle Shot Point Patch: adesivos com microestruturas para espinhas, 9 unidades</t>
+          <t>Collagen Reedle Shot 100: máscara de hidrogel firmadora em 2 passos, 4 unidades</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4663,7 +4661,7 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>48.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
@@ -4672,14 +4670,16 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garlic AC Reedle shot Point Patch</t>
+          <t>Collagen reedle shot 100</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I77" s="4" t="n"/>
+        <v>34.56</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>46.08</v>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-point-patch</t>
+          <t>https://globalvt-cosmetics.com/products/collagen-reedle-shot-100</t>
         </is>
       </c>
       <c r="L77" s="2">
@@ -4702,12 +4702,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MB002983</t>
+          <t>MB002992</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hydrop Reedle Shot 100: máscara de hidrogel hidratante em 2 passos, 4 unidades</t>
+          <t>Garlic AC Reedle Shot Point Patch: adesivos com microestruturas para espinhas, 9 unidades</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>128.9</v>
+        <v>48.9</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
@@ -4725,16 +4725,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hydrop reedle shot 100</t>
+          <t>Garlic AC Reedle shot Point Patch</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="4" t="n">
-        <v>29.18</v>
-      </c>
-      <c r="I78" s="4" t="n">
-        <v>30.72</v>
-      </c>
+        <v>9.5</v>
+      </c>
+      <c r="I78" s="4" t="n"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4742,7 +4740,7 @@
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/hydrop-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-point-patch</t>
         </is>
       </c>
       <c r="L78" s="2">
@@ -4757,12 +4755,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MB002971</t>
+          <t>MB002983</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PDRN Hydrogel Mask: máscara de hidrogel com PDRN vegetal, 4 unidades</t>
+          <t>Hydrop Reedle Shot 100: máscara de hidrogel hidratante em 2 passos, 4 unidades</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4771,7 +4769,7 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>119.9</v>
+        <v>128.9</v>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
@@ -4780,15 +4778,15 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PDRN Hydrogel Mask 4ea</t>
+          <t>Hydrop reedle shot 100</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="4" t="n">
-        <v>18.43</v>
+        <v>29.18</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>23.04</v>
+        <v>30.72</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4797,7 +4795,7 @@
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pdrn-hydrogel-mask-4ea</t>
+          <t>https://globalvt-cosmetics.com/products/hydrop-reedle-shot-100</t>
         </is>
       </c>
       <c r="L79" s="2">
@@ -4812,12 +4810,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MB002999</t>
+          <t>MB002971</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pro Cica Daily Soothing Mask: máscara facial calmante diária com centella, 30 unidades</t>
+          <t>PDRN Hydrogel Mask: máscara de hidrogel com PDRN vegetal, 4 unidades</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4826,7 +4824,7 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>154.9</v>
+        <v>119.9</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
@@ -4835,12 +4833,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pro Cica Reedle Shot 100 2 Step Hydrogel Mask 4ea</t>
+          <t>PDRN Hydrogel Mask 4ea</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="4" t="n">
-        <v>16.13</v>
+        <v>18.43</v>
       </c>
       <c r="I80" s="4" t="n">
         <v>23.04</v>
@@ -4852,7 +4850,7 @@
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pro-cica-reedle-shot-100-2-step-hydrogel-mask-4ea</t>
+          <t>https://globalvt-cosmetics.com/products/pdrn-hydrogel-mask-4ea</t>
         </is>
       </c>
       <c r="L80" s="2">
@@ -4867,12 +4865,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MB002956</t>
+          <t>MB002999</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pro Cica Reedle Shot 100 em sachês: sérum calmante com cica 10 x 2 ml</t>
+          <t>Pro Cica Daily Soothing Mask: máscara facial calmante diária com centella, 30 unidades</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4881,7 +4879,7 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>88.90000000000001</v>
+        <v>154.9</v>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
@@ -4890,15 +4888,15 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pro cica reedle shot 100</t>
+          <t>Pro Cica Reedle Shot 100 2 Step Hydrogel Mask 4ea</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="4" t="n">
-        <v>36.86</v>
+        <v>16.13</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>46.08</v>
+        <v>23.04</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4907,7 +4905,7 @@
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/pro-cica-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/pro-cica-reedle-shot-100-2-step-hydrogel-mask-4ea</t>
         </is>
       </c>
       <c r="L81" s="2">
@@ -4922,12 +4920,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MB002958</t>
+          <t>MB002956</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pro Cica Reedle Shot 100: máscara de hidrogel calmante em 2 passos, 4 unidades</t>
+          <t>Pro Cica Reedle Shot 100 em sachês: sérum calmante com cica 10 x 2 ml</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4936,7 +4934,7 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>119.9</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
@@ -4977,12 +4975,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MB002951</t>
+          <t>MB002958</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Reedle Shot 300 em sachês: sérum booster intensivo 10 x 2 ml</t>
+          <t>Pro Cica Reedle Shot 100: máscara de hidrogel calmante em 2 passos, 4 unidades</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4991,7 +4989,7 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>119.9</v>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
@@ -5000,15 +4998,15 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Reedle Shot 300</t>
+          <t>Pro cica reedle shot 100</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" s="4" t="n">
-        <v>32.2</v>
+        <v>36.86</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>41.28</v>
+        <v>46.08</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -5017,7 +5015,7 @@
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-300</t>
+          <t>https://globalvt-cosmetics.com/products/pro-cica-reedle-shot-100</t>
         </is>
       </c>
       <c r="L83" s="2">
@@ -5032,12 +5030,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MB002941</t>
+          <t>MB002951</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Reti-A Reedle Shot 100 em sachês: sérum com retinol e bakuchiol 10 x 2 ml</t>
+          <t>Reedle Shot 300 em sachês: sérum booster intensivo 10 x 2 ml</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5046,7 +5044,7 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
@@ -5055,15 +5053,15 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Reti-a reedle shot 100</t>
+          <t>Reedle Shot 300</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" s="4" t="n">
-        <v>36.86</v>
+        <v>32.2</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>46.08</v>
+        <v>41.28</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -5072,7 +5070,7 @@
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/reti-a-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/vt-reedle-shot-300</t>
         </is>
       </c>
       <c r="L84" s="2">
@@ -5087,12 +5085,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MB002939</t>
+          <t>MB002941</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Reti-A Reedle Shot 100: máscara de hidrogel em 2 passos, 4 unidades</t>
+          <t>Reti-A Reedle Shot 100 em sachês: sérum com retinol e bakuchiol 10 x 2 ml</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5101,7 +5099,7 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>119.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
@@ -5142,12 +5140,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MB002927</t>
+          <t>MB002939</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vita-Light Reedle Shot 100 em sachês: sérum de vitamina C 10 x 2 ml</t>
+          <t>Reti-A Reedle Shot 100: máscara de hidrogel em 2 passos, 4 unidades</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5156,7 +5154,7 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>119.9</v>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
@@ -5165,12 +5163,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vita-light reedle shot 100</t>
+          <t>Reti-a reedle shot 100</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" s="4" t="n">
-        <v>32.26</v>
+        <v>36.86</v>
       </c>
       <c r="I86" s="4" t="n">
         <v>46.08</v>
@@ -5182,7 +5180,7 @@
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-100</t>
+          <t>https://globalvt-cosmetics.com/products/reti-a-reedle-shot-100</t>
         </is>
       </c>
       <c r="L86" s="2">
@@ -5197,12 +5195,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MB002924</t>
+          <t>MB002927</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Vita-Light Reedle Shot 100: máscara de hidrogel em 2 passos, 4 unidades</t>
+          <t>Vita-Light Reedle Shot 100 em sachês: sérum de vitamina C 10 x 2 ml</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5211,7 +5209,7 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>119.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
@@ -5252,12 +5250,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MB002922</t>
+          <t>MB002924</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vitamin C + Astaxanthin Serum: sérum de vitamina C com cápsulas de astaxantina 30 ml</t>
+          <t>Vita-Light Reedle Shot 100: máscara de hidrogel em 2 passos, 4 unidades</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5266,7 +5264,7 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>155.9</v>
+        <v>119.9</v>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
@@ -5275,15 +5273,15 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitamin C+ Astaxanthin Serum</t>
+          <t>Vita-light reedle shot 100</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" s="4" t="n">
-        <v>22.46</v>
+        <v>32.26</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>24.96</v>
+        <v>46.08</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -5292,7 +5290,7 @@
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/vitamin-c-astaxanthin-serum</t>
+          <t>https://globalvt-cosmetics.com/products/vita-light-reedle-shot-100</t>
         </is>
       </c>
       <c r="L88" s="2">
@@ -5307,12 +5305,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MB002990</t>
+          <t>MB002922</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Adesivo Localizado Garlic AC Reedle Shot</t>
+          <t>Vitamin C + Astaxanthin Serum: sérum de vitamina C com cápsulas de astaxantina 30 ml</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5321,23 +5319,25 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>48.9</v>
+        <v>155.9</v>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garlic AC Reedle shot Spot Patch</t>
+          <t>Vitamin C+ Astaxanthin Serum</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" s="4" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="I89" s="4" t="n"/>
+        <v>22.46</v>
+      </c>
+      <c r="I89" s="4" t="n">
+        <v>24.96</v>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
-          <t>https://globalvt-cosmetics.com/products/garlic-ac-reedle-shot-spot-patch</t>
+          <t>https://globalvt-cosmetics.com/products/vitamin-c-astaxanthin-serum</t>
         </is>
       </c>
       <c r="L89" s="2">
@@ -8473,7 +8473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://globalvt-cosmetics.com · loja "VT Cosmetics official" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
+          <t>Site oficial: https://globalvt-cosmetics.com · loja "VT Cosmetics official" · moeda USD · lido em 30/10/2026 06:08 UTC</t>
         </is>
       </c>
     </row>
